--- a/PBMM_Gap_Analysis.xlsx
+++ b/PBMM_Gap_Analysis.xlsx
@@ -997,23 +997,23 @@
         </is>
       </c>
       <c r="B3" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A3)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A3)</f>
         <v/>
       </c>
       <c r="C3" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D3" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E3" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F3" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G3" s="7">
@@ -1032,23 +1032,23 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A4)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A4)</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D4" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F4" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G4" s="11">
@@ -1067,23 +1067,23 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A5)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A5)</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G5" s="7">
@@ -1102,23 +1102,23 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A6)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A6)</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E6" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G6" s="11">
@@ -1137,23 +1137,23 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A7)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A7)</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G7" s="7">
@@ -1172,23 +1172,23 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A8)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A8)</f>
         <v/>
       </c>
       <c r="C8" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E8" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G8" s="11">
@@ -1207,23 +1207,23 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A9)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A9)</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G9" s="7">
@@ -1242,23 +1242,23 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A10)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A10)</f>
         <v/>
       </c>
       <c r="C10" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D10" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E10" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G10" s="11">
@@ -1277,23 +1277,23 @@
         </is>
       </c>
       <c r="B11" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A11)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A11)</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G11" s="7">
@@ -1312,23 +1312,23 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A12)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D12" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E12" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G12" s="11">
@@ -1347,23 +1347,23 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A13)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A13)</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F13" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G13" s="7">
@@ -1382,23 +1382,23 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A14)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D14" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E14" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G14" s="11">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A15)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A15)</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D15" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E15" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F15" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G15" s="7">
@@ -1452,23 +1452,23 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A16)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A16)</f>
         <v/>
       </c>
       <c r="C16" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D16" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E16" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F16" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G16" s="11">
@@ -1487,23 +1487,23 @@
         </is>
       </c>
       <c r="B17" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A17)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A17)</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D17" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E17" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F17" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G17" s="7">
@@ -1522,23 +1522,23 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A18)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F18" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G18" s="11">
@@ -1557,23 +1557,23 @@
         </is>
       </c>
       <c r="B19" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A19)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A19)</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F19" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G19" s="7">
@@ -1592,23 +1592,23 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A20)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F20" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G20" s="11">
@@ -1627,23 +1627,23 @@
         </is>
       </c>
       <c r="B21" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A21)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A21)</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D21" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E21" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F21" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G21" s="7">
@@ -1662,23 +1662,23 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A22)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F22" s="10">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G22" s="11">
@@ -1697,23 +1697,23 @@
         </is>
       </c>
       <c r="B23" s="6">
-        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A23)</f>
+        <f>COUNTIF('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A23)</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception")</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Under Review")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"In Progress")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Evidence Provided")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Under Review")</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Failed")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Failed")</f>
         <v/>
       </c>
       <c r="F23" s="6">
-        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Not Started")</f>
+        <f>COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Not Started")</f>
         <v/>
       </c>
       <c r="G23" s="7">
@@ -1725,6 +1725,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
@@ -1987,71 +1988,71 @@
         </is>
       </c>
       <c r="B3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R3" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A3,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2062,71 +2063,71 @@
         </is>
       </c>
       <c r="B4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R4" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A4,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2137,71 +2138,71 @@
         </is>
       </c>
       <c r="B5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R5" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A5,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2212,71 +2213,71 @@
         </is>
       </c>
       <c r="B6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R6" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A6,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2287,71 +2288,71 @@
         </is>
       </c>
       <c r="B7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R7" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A7,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2362,71 +2363,71 @@
         </is>
       </c>
       <c r="B8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R8" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A8,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2437,71 +2438,71 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R9" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A9,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2512,71 +2513,71 @@
         </is>
       </c>
       <c r="B10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R10" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A10,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2587,71 +2588,71 @@
         </is>
       </c>
       <c r="B11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R11" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A11,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2662,71 +2663,71 @@
         </is>
       </c>
       <c r="B12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R12" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A12,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2737,71 +2738,71 @@
         </is>
       </c>
       <c r="B13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R13" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A13,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2812,71 +2813,71 @@
         </is>
       </c>
       <c r="B14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R14" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A14,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2887,71 +2888,71 @@
         </is>
       </c>
       <c r="B15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R15" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A15,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -2962,71 +2963,71 @@
         </is>
       </c>
       <c r="B16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R16" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A16,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -3037,71 +3038,71 @@
         </is>
       </c>
       <c r="B17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R17" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A17,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -3112,71 +3113,71 @@
         </is>
       </c>
       <c r="B18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R18" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A18,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -3187,71 +3188,71 @@
         </is>
       </c>
       <c r="B19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R19" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A19,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -3262,71 +3263,71 @@
         </is>
       </c>
       <c r="B20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R20" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A20,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -3337,71 +3338,71 @@
         </is>
       </c>
       <c r="B21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R21" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A21,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -3412,71 +3413,71 @@
         </is>
       </c>
       <c r="B22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R22" s="26">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A22,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -3487,71 +3488,71 @@
         </is>
       </c>
       <c r="B23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AC"),"")</f>
         <v/>
       </c>
       <c r="C23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AT"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AT"),"")</f>
         <v/>
       </c>
       <c r="D23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"AU"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"AU"),"")</f>
         <v/>
       </c>
       <c r="E23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CA"),"")</f>
         <v/>
       </c>
       <c r="F23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CM"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CM"),"")</f>
         <v/>
       </c>
       <c r="G23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"CP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"CP"),"")</f>
         <v/>
       </c>
       <c r="H23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IA"),"")</f>
         <v/>
       </c>
       <c r="I23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"IR"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"IR"),"")</f>
         <v/>
       </c>
       <c r="J23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MA"),"")</f>
         <v/>
       </c>
       <c r="K23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"MP"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"MP"),"")</f>
         <v/>
       </c>
       <c r="L23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PE"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PE"),"")</f>
         <v/>
       </c>
       <c r="M23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PL"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PL"),"")</f>
         <v/>
       </c>
       <c r="N23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"PS"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"PS"),"")</f>
         <v/>
       </c>
       <c r="O23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"RA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"RA"),"")</f>
         <v/>
       </c>
       <c r="P23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SA"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SA"),"")</f>
         <v/>
       </c>
       <c r="Q23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SC"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SC"),"")</f>
         <v/>
       </c>
       <c r="R23" s="24">
-        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G:$G,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C:$C,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D:$D,"SI"),"")</f>
+        <f>IFERROR(1-(COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Passed")+COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI",'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$G$3:$G$1275,"Accepted Exception"))/COUNTIFS('[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$C$3:$C$1275,$A23,'[PBMM_Master_Tracker_v2.xlsx]TRACKER'!$D$3:$D$1275,"SI"),"")</f>
         <v/>
       </c>
     </row>
@@ -5288,11 +5289,11 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF('REMEDIATION PLAN'!H:H,A4)</f>
+        <f>COUNTIF('REMEDIATION PLAN'!H$2:H$102,A4)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIFS('REMEDIATION PLAN'!H:H,A4,'REMEDIATION PLAN'!K:K,"Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!H$2:H$102,A4,'REMEDIATION PLAN'!K$2:K$102,"Completed")</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -5307,11 +5308,11 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF('REMEDIATION PLAN'!H:H,A5)</f>
+        <f>COUNTIF('REMEDIATION PLAN'!H$2:H$102,A5)</f>
         <v/>
       </c>
       <c r="C5" s="10">
-        <f>COUNTIFS('REMEDIATION PLAN'!H:H,A5,'REMEDIATION PLAN'!K:K,"Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!H$2:H$102,A5,'REMEDIATION PLAN'!K$2:K$102,"Completed")</f>
         <v/>
       </c>
       <c r="D5" s="10">
@@ -5326,11 +5327,11 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF('REMEDIATION PLAN'!H:H,A6)</f>
+        <f>COUNTIF('REMEDIATION PLAN'!H$2:H$102,A6)</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>COUNTIFS('REMEDIATION PLAN'!H:H,A6,'REMEDIATION PLAN'!K:K,"Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!H$2:H$102,A6,'REMEDIATION PLAN'!K$2:K$102,"Completed")</f>
         <v/>
       </c>
       <c r="D6" s="6">
@@ -5345,11 +5346,11 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF('REMEDIATION PLAN'!H:H,A7)</f>
+        <f>COUNTIF('REMEDIATION PLAN'!H$2:H$102,A7)</f>
         <v/>
       </c>
       <c r="C7" s="10">
-        <f>COUNTIFS('REMEDIATION PLAN'!H:H,A7,'REMEDIATION PLAN'!K:K,"Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!H$2:H$102,A7,'REMEDIATION PLAN'!K$2:K$102,"Completed")</f>
         <v/>
       </c>
       <c r="D7" s="10">
@@ -5376,6 +5377,7 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
@@ -5394,7 +5396,7 @@
         </is>
       </c>
       <c r="B11" s="6">
-        <f>COUNTIF('REMEDIATION PLAN'!K:K,A11)</f>
+        <f>COUNTIF('REMEDIATION PLAN'!K$2:K$102,A11)</f>
         <v/>
       </c>
     </row>
@@ -5405,7 +5407,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF('REMEDIATION PLAN'!K:K,A12)</f>
+        <f>COUNTIF('REMEDIATION PLAN'!K$2:K$102,A12)</f>
         <v/>
       </c>
     </row>
@@ -5416,7 +5418,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF('REMEDIATION PLAN'!K:K,A13)</f>
+        <f>COUNTIF('REMEDIATION PLAN'!K$2:K$102,A13)</f>
         <v/>
       </c>
     </row>
@@ -5427,7 +5429,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF('REMEDIATION PLAN'!K:K,A14)</f>
+        <f>COUNTIF('REMEDIATION PLAN'!K$2:K$102,A14)</f>
         <v/>
       </c>
     </row>
@@ -5438,10 +5440,11 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF('REMEDIATION PLAN'!K:K,A15)</f>
-        <v/>
-      </c>
-    </row>
+        <f>COUNTIF('REMEDIATION PLAN'!K$2:K$102,A15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
@@ -5453,6 +5456,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
@@ -5493,15 +5497,15 @@
         </is>
       </c>
       <c r="B21" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A21,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A21,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C21" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A21,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A21,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D21" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A21,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A21,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A21,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A21,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5512,15 +5516,15 @@
         </is>
       </c>
       <c r="B22" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A22,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A22,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C22" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A22,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A22,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D22" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A22,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A22,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A22,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A22,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5531,15 +5535,15 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A23,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A23,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C23" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A23,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A23,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D23" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A23,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A23,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A23,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A23,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5550,15 +5554,15 @@
         </is>
       </c>
       <c r="B24" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A24,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A24,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C24" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A24,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A24,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D24" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A24,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A24,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A24,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A24,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5569,15 +5573,15 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A25,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A25,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C25" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A25,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A25,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D25" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A25,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A25,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A25,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A25,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5588,15 +5592,15 @@
         </is>
       </c>
       <c r="B26" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A26,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A26,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C26" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A26,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A26,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D26" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A26,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A26,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A26,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A26,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5607,15 +5611,15 @@
         </is>
       </c>
       <c r="B27" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A27,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A27,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C27" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A27,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A27,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D27" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A27,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A27,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A27,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A27,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5626,15 +5630,15 @@
         </is>
       </c>
       <c r="B28" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A28,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A28,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C28" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A28,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A28,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D28" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A28,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A28,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A28,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A28,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5645,15 +5649,15 @@
         </is>
       </c>
       <c r="B29" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A29,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A29,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C29" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A29,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A29,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D29" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A29,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A29,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A29,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A29,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5664,15 +5668,15 @@
         </is>
       </c>
       <c r="B30" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A30,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A30,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C30" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A30,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A30,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D30" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A30,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A30,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A30,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A30,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5683,15 +5687,15 @@
         </is>
       </c>
       <c r="B31" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A31,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A31,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C31" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A31,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A31,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D31" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A31,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A31,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A31,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A31,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5702,15 +5706,15 @@
         </is>
       </c>
       <c r="B32" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A32,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A32,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C32" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A32,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A32,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D32" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A32,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A32,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A32,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A32,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5721,15 +5725,15 @@
         </is>
       </c>
       <c r="B33" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A33,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A33,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C33" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A33,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A33,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D33" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A33,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A33,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A33,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A33,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5740,15 +5744,15 @@
         </is>
       </c>
       <c r="B34" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A34,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A34,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C34" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A34,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A34,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D34" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A34,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A34,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A34,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A34,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5759,15 +5763,15 @@
         </is>
       </c>
       <c r="B35" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A35,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A35,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C35" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A35,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A35,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D35" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A35,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A35,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A35,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A35,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5778,15 +5782,15 @@
         </is>
       </c>
       <c r="B36" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A36,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A36,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C36" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A36,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A36,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D36" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A36,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A36,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A36,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A36,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5797,15 +5801,15 @@
         </is>
       </c>
       <c r="B37" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A37,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A37,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C37" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A37,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A37,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D37" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A37,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A37,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A37,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A37,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5816,15 +5820,15 @@
         </is>
       </c>
       <c r="B38" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A38,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A38,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C38" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A38,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A38,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D38" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A38,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A38,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A38,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A38,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5835,15 +5839,15 @@
         </is>
       </c>
       <c r="B39" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A39,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A39,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C39" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A39,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A39,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D39" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A39,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A39,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A39,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A39,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5854,15 +5858,15 @@
         </is>
       </c>
       <c r="B40" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A40,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A40,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C40" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A40,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A40,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D40" s="29">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A40,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A40,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A40,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A40,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
@@ -5873,15 +5877,15 @@
         </is>
       </c>
       <c r="B41" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A41,'REMEDIATION PLAN'!H:H,"Critical",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A41,'REMEDIATION PLAN'!H$2:H$102,"Critical",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="C41" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A41,'REMEDIATION PLAN'!H:H,"High",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A41,'REMEDIATION PLAN'!H$2:H$102,"High",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
       <c r="D41" s="27">
-        <f>COUNTIFS('REMEDIATION PLAN'!D:D,A41,'REMEDIATION PLAN'!H:H,"Medium",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D:D,A41,'REMEDIATION PLAN'!H:H,"Low",'REMEDIATION PLAN'!K:K,"&lt;&gt;Completed")</f>
+        <f>COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A41,'REMEDIATION PLAN'!H$2:H$102,"Medium",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")+COUNTIFS('REMEDIATION PLAN'!D$2:D$102,A41,'REMEDIATION PLAN'!H$2:H$102,"Low",'REMEDIATION PLAN'!K$2:K$102,"&lt;&gt;Completed")</f>
         <v/>
       </c>
     </row>
